--- a/data/sars/atlantic/tables/Atlantic_2002_Table1.xlsx
+++ b/data/sars/atlantic/tables/Atlantic_2002_Table1.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/atlantic/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C66C1B-8E5F-6F43-BD5F-64F5D737AB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73B1FFA-76D3-9048-868B-2C13D4F84765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="500" windowWidth="24720" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="500" windowWidth="33800" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 1'!$A$1:$M$58</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="83">
   <si>
     <t>species</t>
   </si>
@@ -253,168 +256,19 @@
     <t>Risso’s dolphin</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1.8 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1.0 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Y
-m</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">3.0 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Y
-a,m,p</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1.6 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">2.6 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">2.4 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Y
-p</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">373 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">2,419 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>7</t>
-    </r>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>a, m, p</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>m, p</t>
+  </si>
+  <si>
+    <t>p</t>
   </si>
   <si>
     <r>
@@ -424,8 +278,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Mesoplodon
-</t>
+      <t xml:space="preserve">Mesoplodon </t>
     </r>
     <r>
       <rPr>
@@ -436,173 +289,6 @@
       <t>beaked whales</t>
     </r>
   </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Y
-m, p</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">11,343 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">199 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>9</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">27,785 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">7.8 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>11</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>11</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">24,897 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>N/A</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>14</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Y
-a, m, p</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">459 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>12</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">435 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>12</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">321,222 </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>13</t>
-    </r>
-  </si>
 </sst>
 </file>
 
@@ -611,7 +297,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -636,18 +322,6 @@
       <family val="2"/>
     </font>
     <font>
-      <vertAlign val="superscript"/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <name val="Arial"/>
@@ -662,27 +336,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -693,35 +352,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1028,21 +687,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="22.3984375" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="61.3984375" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="28" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="22.3984375" style="3"/>
+    <col min="1" max="1" width="34.796875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="48.796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.19921875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.19921875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="61.3984375" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" x14ac:dyDescent="0.15">
@@ -1080,11 +739,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2"/>
-    </row>
-    <row r="2" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -1097,33 +758,35 @@
       <c r="D2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="5">
         <v>291</v>
       </c>
-      <c r="F2" s="7">
-        <v>0</v>
-      </c>
-      <c r="G2" s="8">
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+      <c r="G2" s="6">
         <v>0.1</v>
       </c>
-      <c r="H2" s="8">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>78</v>
+      <c r="H2" s="6">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="J2" s="4">
+        <v>1</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
@@ -1136,33 +799,35 @@
       <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="5">
         <v>647</v>
       </c>
-      <c r="F3" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G3" s="8">
+      <c r="F3" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G3" s="6">
         <v>0.1</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="6">
         <v>1.3</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="J3" s="9">
+      <c r="I3" s="4">
+        <v>3</v>
+      </c>
+      <c r="J3" s="8">
         <v>2.82</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="M3" s="5"/>
-    </row>
-    <row r="4" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+      <c r="L3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>19</v>
       </c>
@@ -1175,31 +840,33 @@
       <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <v>2362</v>
       </c>
-      <c r="F4" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G4" s="8">
+      <c r="F4" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G4" s="6">
         <v>0.1</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="6">
         <v>4.7</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="J4" s="9">
+      <c r="I4" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="J4" s="8">
         <v>0.43</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M4" s="5"/>
     </row>
     <row r="5" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
@@ -1217,19 +884,19 @@
       <c r="E5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G5" s="8">
+      <c r="F5" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G5" s="6">
         <v>0.1</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="9">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9">
+      <c r="I5" s="8">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="s">
@@ -1238,9 +905,9 @@
       <c r="L5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="M5" s="5"/>
-    </row>
-    <row r="6" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+      <c r="M5" s="7"/>
+    </row>
+    <row r="6" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
@@ -1253,33 +920,35 @@
       <c r="D6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <v>3515</v>
       </c>
-      <c r="F6" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G6" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H6" s="7">
+      <c r="F6" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="5">
         <v>35</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>84</v>
+      <c r="I6" s="4">
+        <v>2.6</v>
+      </c>
+      <c r="J6" s="4">
+        <v>2.4</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M6" s="5"/>
-    </row>
-    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    </row>
+    <row r="7" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
@@ -1292,33 +961,35 @@
       <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <v>308</v>
       </c>
-      <c r="F7" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G7" s="8">
+      <c r="F7" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G7" s="6">
         <v>0.1</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="6">
         <v>0.2</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <v>0</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="M7" s="5"/>
-    </row>
-    <row r="8" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+      <c r="L7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
         <v>27</v>
       </c>
@@ -1331,33 +1002,35 @@
       <c r="D8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <v>3505</v>
       </c>
-      <c r="F8" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G8" s="8">
+      <c r="F8" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G8" s="6">
         <v>0.1</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="6">
         <v>7</v>
       </c>
-      <c r="I8" s="9">
-        <v>0</v>
-      </c>
-      <c r="J8" s="8">
+      <c r="I8" s="8">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6">
         <v>0.2</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M8" s="5"/>
-    </row>
-    <row r="9" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    </row>
+    <row r="9" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>29</v>
       </c>
@@ -1370,33 +1043,35 @@
       <c r="D9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F9" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G9" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H9" s="8">
+      <c r="E9" s="4">
+        <v>373</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="6">
         <v>3.7</v>
       </c>
-      <c r="I9" s="7">
-        <v>0</v>
-      </c>
-      <c r="J9" s="7">
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
         <v>0</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M9" s="5"/>
-    </row>
-    <row r="10" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    </row>
+    <row r="10" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
         <v>31</v>
       </c>
@@ -1409,31 +1084,33 @@
       <c r="D10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F10" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G10" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H10" s="8">
+      <c r="E10" s="4">
+        <v>373</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H10" s="6">
         <v>3.7</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="5">
         <v>6</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="5">
         <v>6</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M10" s="5"/>
     </row>
     <row r="11" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
@@ -1451,7 +1128,7 @@
       <c r="E11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <v>0.04</v>
       </c>
       <c r="G11" s="4" t="s">
@@ -1460,10 +1137,10 @@
       <c r="H11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="9">
-        <v>0</v>
-      </c>
-      <c r="J11" s="9">
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
         <v>0</v>
       </c>
       <c r="K11" s="4" t="s">
@@ -1472,7 +1149,7 @@
       <c r="L11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="5"/>
+      <c r="M11" s="7"/>
     </row>
     <row r="12" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
@@ -1487,22 +1164,22 @@
       <c r="D12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <v>6</v>
       </c>
-      <c r="F12" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G12" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H12" s="8">
+      <c r="F12" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="6">
         <v>0.1</v>
       </c>
-      <c r="I12" s="9">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9">
+      <c r="I12" s="8">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8">
         <v>0</v>
       </c>
       <c r="K12" s="4" t="s">
@@ -1511,7 +1188,7 @@
       <c r="L12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M12" s="5"/>
+      <c r="M12" s="7"/>
     </row>
     <row r="13" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
@@ -1529,7 +1206,7 @@
       <c r="E13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="8">
         <v>0.04</v>
       </c>
       <c r="G13" s="4" t="s">
@@ -1538,10 +1215,10 @@
       <c r="H13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="9">
-        <v>0</v>
-      </c>
-      <c r="J13" s="9">
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
         <v>0</v>
       </c>
       <c r="K13" s="4" t="s">
@@ -1550,9 +1227,9 @@
       <c r="L13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M13" s="5"/>
-    </row>
-    <row r="14" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+      <c r="M13" s="7"/>
+    </row>
+    <row r="14" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
         <v>37</v>
       </c>
@@ -1565,35 +1242,37 @@
       <c r="D14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G14" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H14" s="7">
+      <c r="E14" s="10">
+        <v>2419</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="5">
         <v>24</v>
       </c>
-      <c r="I14" s="7">
-        <v>0</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>88</v>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M14" s="5"/>
-    </row>
-    <row r="15" spans="1:13" ht="30" x14ac:dyDescent="0.15">
-      <c r="A15" s="6" t="s">
-        <v>89</v>
+    </row>
+    <row r="15" spans="1:13" ht="15" x14ac:dyDescent="0.15">
+      <c r="A15" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>13</v>
@@ -1604,33 +1283,35 @@
       <c r="D15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F15" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G15" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H15" s="7">
+      <c r="E15" s="10">
+        <v>2419</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="5">
         <v>24</v>
       </c>
-      <c r="I15" s="7">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>88</v>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="L15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M15" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M15" s="5"/>
-    </row>
-    <row r="16" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    </row>
+    <row r="16" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
         <v>38</v>
       </c>
@@ -1643,33 +1324,35 @@
       <c r="D16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <v>22916</v>
       </c>
-      <c r="F16" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G16" s="9">
+      <c r="F16" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G16" s="8">
         <v>0.48</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="5">
         <v>220</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="5">
         <v>51</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="5">
         <v>51</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L16" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="M16" s="5"/>
-    </row>
-    <row r="17" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+      <c r="L16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
         <v>39</v>
       </c>
@@ -1682,33 +1365,35 @@
       <c r="D17" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G17" s="9">
+      <c r="E17" s="10">
+        <v>11343</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G17" s="8">
         <v>0.48</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="5">
         <v>108</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>92</v>
+      <c r="I17" s="4">
+        <v>199</v>
+      </c>
+      <c r="J17" s="4">
+        <v>199</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M17" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M17" s="5"/>
-    </row>
-    <row r="18" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    </row>
+    <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
         <v>40</v>
       </c>
@@ -1721,33 +1406,35 @@
       <c r="D18" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G18" s="9">
+      <c r="E18" s="10">
+        <v>11343</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G18" s="8">
         <v>0.48</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="5">
         <v>108</v>
       </c>
-      <c r="I18" s="7">
-        <v>1999</v>
-      </c>
-      <c r="J18" s="7">
-        <v>1999</v>
+      <c r="I18" s="5">
+        <v>199</v>
+      </c>
+      <c r="J18" s="5">
+        <v>199</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M18" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M18" s="5"/>
-    </row>
-    <row r="19" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    </row>
+    <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
         <v>41</v>
       </c>
@@ -1760,31 +1447,33 @@
       <c r="D19" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <v>37904</v>
       </c>
-      <c r="F19" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G19" s="9">
+      <c r="F19" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G19" s="8">
         <v>0.48</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="5">
         <v>364</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="5">
         <v>118</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="5">
         <v>118</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L19" s="6" t="s">
+      <c r="L19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M19" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M19" s="5"/>
     </row>
     <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
@@ -1802,7 +1491,7 @@
       <c r="E20" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="8">
         <v>0.04</v>
       </c>
       <c r="G20" s="4" t="s">
@@ -1811,10 +1500,10 @@
       <c r="H20" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I20" s="9">
-        <v>0</v>
-      </c>
-      <c r="J20" s="9">
+      <c r="I20" s="8">
+        <v>0</v>
+      </c>
+      <c r="J20" s="8">
         <v>0</v>
       </c>
       <c r="K20" s="4" t="s">
@@ -1823,9 +1512,9 @@
       <c r="L20" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="M20" s="5"/>
-    </row>
-    <row r="21" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+      <c r="M20" s="7"/>
+    </row>
+    <row r="21" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
         <v>44</v>
       </c>
@@ -1838,32 +1527,35 @@
       <c r="D21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <v>23655</v>
       </c>
-      <c r="F21" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G21" s="9">
+      <c r="F21" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G21" s="8">
         <v>0.48</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="5">
         <v>227</v>
       </c>
-      <c r="I21" s="7">
+      <c r="I21" s="5">
         <v>375</v>
       </c>
-      <c r="J21" s="7">
+      <c r="J21" s="5">
         <v>375</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L21" s="6" t="s">
+      <c r="L21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="16" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
         <v>45</v>
       </c>
@@ -1876,23 +1568,23 @@
       <c r="D22" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F22" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G22" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H22" s="7">
+      <c r="E22" s="10">
+        <v>27785</v>
+      </c>
+      <c r="F22" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G22" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H22" s="5">
         <v>278</v>
       </c>
-      <c r="I22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>94</v>
+      <c r="I22" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="J22" s="4">
+        <v>7.8</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>25</v>
@@ -1901,7 +1593,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
         <v>47</v>
       </c>
@@ -1914,28 +1606,31 @@
       <c r="D23" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="9">
         <v>8450</v>
       </c>
-      <c r="F23" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G23" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H23" s="7">
+      <c r="F23" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G23" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H23" s="5">
         <v>84</v>
       </c>
-      <c r="I23" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>95</v>
+      <c r="I23" s="2">
+        <v>1</v>
+      </c>
+      <c r="J23" s="2">
+        <v>1</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L23" s="6" t="s">
+      <c r="L23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M23" s="7" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1952,22 +1647,22 @@
       <c r="D24" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="9">
         <v>44500</v>
       </c>
-      <c r="F24" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G24" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H24" s="7">
+      <c r="F24" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G24" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H24" s="5">
         <v>445</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="6">
         <v>7.3</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="6">
         <v>7.3</v>
       </c>
       <c r="K24" s="4" t="s">
@@ -2002,10 +1697,10 @@
       <c r="H25" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="8">
         <v>0.31</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="8">
         <v>0.31</v>
       </c>
       <c r="K25" s="4" t="s">
@@ -2015,7 +1710,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
         <v>50</v>
       </c>
@@ -2028,32 +1723,35 @@
       <c r="D26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G26" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H26" s="7">
+      <c r="E26" s="10">
+        <v>24897</v>
+      </c>
+      <c r="F26" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G26" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H26" s="5">
         <v>249</v>
       </c>
-      <c r="I26" s="7">
+      <c r="I26" s="5">
         <v>27</v>
       </c>
-      <c r="J26" s="7">
+      <c r="J26" s="5">
         <v>27</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L26" s="6" t="s">
+      <c r="L26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M26" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
         <v>50</v>
       </c>
@@ -2067,31 +1765,34 @@
         <v>30</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F27" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G27" s="8">
+        <v>22</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G27" s="6">
         <v>0.5</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L27" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+      <c r="L27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
         <v>53</v>
       </c>
@@ -2104,32 +1805,35 @@
       <c r="D28" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="9">
         <v>74695</v>
       </c>
-      <c r="F28" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G28" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H28" s="7">
+      <c r="F28" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G28" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H28" s="5">
         <v>747</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>100</v>
+      <c r="I28" s="4">
+        <v>459</v>
+      </c>
+      <c r="J28" s="4">
+        <v>435</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L28" s="6" t="s">
+      <c r="L28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M28" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="4" t="s">
         <v>55</v>
       </c>
@@ -2142,32 +1846,35 @@
       <c r="D29" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="9">
         <v>30990</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="8">
         <v>0.12</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="6">
         <v>1</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="9">
         <v>1859</v>
       </c>
-      <c r="I29" s="7">
+      <c r="I29" s="5">
         <v>857</v>
       </c>
-      <c r="J29" s="7">
+      <c r="J29" s="5">
         <v>843</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L29" s="6" t="s">
+      <c r="L29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M29" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
         <v>56</v>
       </c>
@@ -2192,20 +1899,23 @@
       <c r="H30" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="I30" s="7">
+      <c r="I30" s="5">
         <v>307</v>
       </c>
-      <c r="J30" s="7">
+      <c r="J30" s="5">
         <v>118</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L30" s="6" t="s">
+      <c r="L30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M30" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A31" s="4" t="s">
         <v>58</v>
       </c>
@@ -2230,16 +1940,19 @@
       <c r="H31" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I31" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="J31" s="7">
+      <c r="I31" s="10">
+        <v>321222</v>
+      </c>
+      <c r="J31" s="5">
         <v>111</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L31" s="6" t="s">
+      <c r="L31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M31" s="7" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2268,10 +1981,10 @@
       <c r="H32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I32" s="8">
+      <c r="I32" s="6">
         <v>5.6</v>
       </c>
-      <c r="J32" s="8">
+      <c r="J32" s="6">
         <v>5.6</v>
       </c>
       <c r="K32" s="4" t="s">
@@ -2294,22 +2007,22 @@
       <c r="D33" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="5">
         <v>411</v>
       </c>
-      <c r="F33" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G33" s="8">
+      <c r="F33" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G33" s="6">
         <v>0.1</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="6">
         <v>0.8</v>
       </c>
-      <c r="I33" s="9">
-        <v>0</v>
-      </c>
-      <c r="J33" s="9">
+      <c r="I33" s="8">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8">
         <v>0</v>
       </c>
       <c r="K33" s="4" t="s">
@@ -2332,22 +2045,22 @@
       <c r="D34" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="5">
         <v>17</v>
       </c>
-      <c r="F34" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G34" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H34" s="8">
+      <c r="F34" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G34" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H34" s="6">
         <v>0.2</v>
       </c>
-      <c r="I34" s="9">
-        <v>0</v>
-      </c>
-      <c r="J34" s="9">
+      <c r="I34" s="8">
+        <v>0</v>
+      </c>
+      <c r="J34" s="8">
         <v>0</v>
       </c>
       <c r="K34" s="4" t="s">
@@ -2370,22 +2083,22 @@
       <c r="D35" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="5">
         <v>20</v>
       </c>
-      <c r="F35" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G35" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H35" s="8">
+      <c r="F35" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G35" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H35" s="6">
         <v>0.2</v>
       </c>
-      <c r="I35" s="9">
-        <v>0</v>
-      </c>
-      <c r="J35" s="9">
+      <c r="I35" s="8">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8">
         <v>0</v>
       </c>
       <c r="K35" s="4" t="s">
@@ -2420,10 +2133,10 @@
       <c r="H36" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="9">
-        <v>0</v>
-      </c>
-      <c r="J36" s="9">
+      <c r="I36" s="8">
+        <v>0</v>
+      </c>
+      <c r="J36" s="8">
         <v>0</v>
       </c>
       <c r="K36" s="4" t="s">
@@ -2458,10 +2171,10 @@
       <c r="H37" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="9">
-        <v>0</v>
-      </c>
-      <c r="J37" s="9">
+      <c r="I37" s="8">
+        <v>0</v>
+      </c>
+      <c r="J37" s="8">
         <v>0</v>
       </c>
       <c r="K37" s="4" t="s">
@@ -2471,7 +2184,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
         <v>50</v>
       </c>
@@ -2484,22 +2197,22 @@
       <c r="D38" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="9">
         <v>43233</v>
       </c>
-      <c r="F38" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G38" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H38" s="7">
+      <c r="F38" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G38" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H38" s="5">
         <v>432</v>
       </c>
-      <c r="I38" s="8">
+      <c r="I38" s="6">
         <v>2.8</v>
       </c>
-      <c r="J38" s="8">
+      <c r="J38" s="6">
         <v>2.8</v>
       </c>
       <c r="K38" s="4" t="s">
@@ -2509,7 +2222,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
         <v>50</v>
       </c>
@@ -2522,22 +2235,22 @@
       <c r="D39" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E39" s="10">
+      <c r="E39" s="9">
         <v>4530</v>
       </c>
-      <c r="F39" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G39" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H39" s="7">
+      <c r="F39" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G39" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H39" s="5">
         <v>45</v>
       </c>
-      <c r="I39" s="8">
+      <c r="I39" s="6">
         <v>2.8</v>
       </c>
-      <c r="J39" s="8">
+      <c r="J39" s="6">
         <v>2.8</v>
       </c>
       <c r="K39" s="4" t="s">
@@ -2560,22 +2273,22 @@
       <c r="D40" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E40" s="10">
+      <c r="E40" s="9">
         <v>2938</v>
       </c>
-      <c r="F40" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G40" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H40" s="7">
+      <c r="F40" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G40" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H40" s="5">
         <v>29</v>
       </c>
-      <c r="I40" s="7">
+      <c r="I40" s="5">
         <v>13</v>
       </c>
-      <c r="J40" s="7">
+      <c r="J40" s="5">
         <v>13</v>
       </c>
       <c r="K40" s="4" t="s">
@@ -2598,22 +2311,22 @@
       <c r="D41" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="9">
         <v>3518</v>
       </c>
-      <c r="F41" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G41" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H41" s="7">
+      <c r="F41" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G41" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H41" s="5">
         <v>35</v>
       </c>
-      <c r="I41" s="7">
+      <c r="I41" s="5">
         <v>10</v>
       </c>
-      <c r="J41" s="7">
+      <c r="J41" s="5">
         <v>10</v>
       </c>
       <c r="K41" s="4" t="s">
@@ -2637,22 +2350,22 @@
       <c r="D42" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="9">
         <v>8963</v>
       </c>
-      <c r="F42" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G42" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H42" s="7">
+      <c r="F42" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G42" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H42" s="5">
         <v>90</v>
       </c>
-      <c r="I42" s="7">
+      <c r="I42" s="5">
         <v>8</v>
       </c>
-      <c r="J42" s="7">
+      <c r="J42" s="5">
         <v>8</v>
       </c>
       <c r="K42" s="4" t="s">
@@ -2663,7 +2376,7 @@
       </c>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
         <v>50</v>
       </c>
@@ -2676,16 +2389,16 @@
       <c r="D43" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E43" s="9">
         <v>3933</v>
       </c>
-      <c r="F43" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G43" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H43" s="7">
+      <c r="F43" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G43" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H43" s="5">
         <v>39</v>
       </c>
       <c r="I43" s="4" t="s">
@@ -2715,22 +2428,22 @@
       <c r="D44" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E44" s="10">
+      <c r="E44" s="9">
         <v>2255</v>
       </c>
-      <c r="F44" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G44" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H44" s="7">
+      <c r="F44" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G44" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H44" s="5">
         <v>23</v>
       </c>
-      <c r="I44" s="8">
+      <c r="I44" s="6">
         <v>1.5</v>
       </c>
-      <c r="J44" s="8">
+      <c r="J44" s="6">
         <v>1.5</v>
       </c>
       <c r="K44" s="4" t="s">
@@ -2754,22 +2467,22 @@
       <c r="D45" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E45" s="10">
+      <c r="E45" s="9">
         <v>26510</v>
       </c>
-      <c r="F45" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G45" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H45" s="7">
+      <c r="F45" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G45" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H45" s="5">
         <v>265</v>
       </c>
-      <c r="I45" s="8">
+      <c r="I45" s="6">
         <v>1.5</v>
       </c>
-      <c r="J45" s="8">
+      <c r="J45" s="6">
         <v>1.5</v>
       </c>
       <c r="K45" s="4" t="s">
@@ -2793,22 +2506,22 @@
       <c r="D46" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E46" s="10">
+      <c r="E46" s="9">
         <v>3409</v>
       </c>
-      <c r="F46" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G46" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H46" s="7">
+      <c r="F46" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G46" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H46" s="5">
         <v>34</v>
       </c>
-      <c r="I46" s="9">
-        <v>0</v>
-      </c>
-      <c r="J46" s="9">
+      <c r="I46" s="8">
+        <v>0</v>
+      </c>
+      <c r="J46" s="8">
         <v>0</v>
       </c>
       <c r="K46" s="4" t="s">
@@ -2817,7 +2530,7 @@
       <c r="L46" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M46" s="5"/>
+      <c r="M46" s="7"/>
     </row>
     <row r="47" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A47" s="4" t="s">
@@ -2832,22 +2545,22 @@
       <c r="D47" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E47" s="10">
+      <c r="E47" s="9">
         <v>4465</v>
       </c>
-      <c r="F47" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G47" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H47" s="7">
+      <c r="F47" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G47" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H47" s="5">
         <v>45</v>
       </c>
-      <c r="I47" s="9">
-        <v>0</v>
-      </c>
-      <c r="J47" s="9">
+      <c r="I47" s="8">
+        <v>0</v>
+      </c>
+      <c r="J47" s="8">
         <v>0</v>
       </c>
       <c r="K47" s="4" t="s">
@@ -2871,22 +2584,22 @@
       <c r="D48" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E48" s="5">
         <v>660</v>
       </c>
-      <c r="F48" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G48" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H48" s="8">
+      <c r="F48" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G48" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H48" s="6">
         <v>6.6</v>
       </c>
-      <c r="I48" s="9">
-        <v>0</v>
-      </c>
-      <c r="J48" s="9">
+      <c r="I48" s="8">
+        <v>0</v>
+      </c>
+      <c r="J48" s="8">
         <v>0</v>
       </c>
       <c r="K48" s="4" t="s">
@@ -2910,22 +2623,22 @@
       <c r="D49" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E49" s="10">
+      <c r="E49" s="9">
         <v>4120</v>
       </c>
-      <c r="F49" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G49" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H49" s="7">
+      <c r="F49" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G49" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H49" s="5">
         <v>41</v>
       </c>
-      <c r="I49" s="9">
-        <v>0</v>
-      </c>
-      <c r="J49" s="9">
+      <c r="I49" s="8">
+        <v>0</v>
+      </c>
+      <c r="J49" s="8">
         <v>0</v>
       </c>
       <c r="K49" s="4" t="s">
@@ -2949,22 +2662,22 @@
       <c r="D50" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E50" s="7">
+      <c r="E50" s="5">
         <v>66</v>
       </c>
-      <c r="F50" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G50" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H50" s="8">
+      <c r="F50" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G50" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H50" s="6">
         <v>0.7</v>
       </c>
-      <c r="I50" s="9">
-        <v>0</v>
-      </c>
-      <c r="J50" s="9">
+      <c r="I50" s="8">
+        <v>0</v>
+      </c>
+      <c r="J50" s="8">
         <v>0</v>
       </c>
       <c r="K50" s="4" t="s">
@@ -2973,7 +2686,7 @@
       <c r="L50" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M50" s="5"/>
+      <c r="M50" s="7"/>
     </row>
     <row r="51" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="s">
@@ -2988,22 +2701,22 @@
       <c r="D51" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E51" s="7">
+      <c r="E51" s="5">
         <v>197</v>
       </c>
-      <c r="F51" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G51" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H51" s="8">
+      <c r="F51" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G51" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H51" s="6">
         <v>2</v>
       </c>
-      <c r="I51" s="9">
-        <v>0</v>
-      </c>
-      <c r="J51" s="9">
+      <c r="I51" s="8">
+        <v>0</v>
+      </c>
+      <c r="J51" s="8">
         <v>0</v>
       </c>
       <c r="K51" s="4" t="s">
@@ -3027,22 +2740,22 @@
       <c r="D52" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E52" s="7">
+      <c r="E52" s="5">
         <v>236</v>
       </c>
-      <c r="F52" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G52" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H52" s="8">
+      <c r="F52" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G52" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H52" s="6">
         <v>2.4</v>
       </c>
-      <c r="I52" s="9">
-        <v>0</v>
-      </c>
-      <c r="J52" s="9">
+      <c r="I52" s="8">
+        <v>0</v>
+      </c>
+      <c r="J52" s="8">
         <v>0</v>
       </c>
       <c r="K52" s="4" t="s">
@@ -3066,22 +2779,22 @@
       <c r="D53" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E53" s="7">
+      <c r="E53" s="5">
         <v>285</v>
       </c>
-      <c r="F53" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G53" s="9">
+      <c r="F53" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G53" s="8">
         <v>0.05</v>
       </c>
-      <c r="H53" s="8">
+      <c r="H53" s="6">
         <v>2.8</v>
       </c>
-      <c r="I53" s="9">
-        <v>0</v>
-      </c>
-      <c r="J53" s="9">
+      <c r="I53" s="8">
+        <v>0</v>
+      </c>
+      <c r="J53" s="8">
         <v>0</v>
       </c>
       <c r="K53" s="4" t="s">
@@ -3108,7 +2821,7 @@
       <c r="E54" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F54" s="9">
+      <c r="F54" s="8">
         <v>0.04</v>
       </c>
       <c r="G54" s="4" t="s">
@@ -3117,10 +2830,10 @@
       <c r="H54" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I54" s="9">
-        <v>0</v>
-      </c>
-      <c r="J54" s="9">
+      <c r="I54" s="8">
+        <v>0</v>
+      </c>
+      <c r="J54" s="8">
         <v>0</v>
       </c>
       <c r="K54" s="4" t="s">
@@ -3129,7 +2842,7 @@
       <c r="L54" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="M54" s="5"/>
+      <c r="M54" s="7"/>
     </row>
     <row r="55" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A55" s="4" t="s">
@@ -3147,7 +2860,7 @@
       <c r="E55" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F55" s="9">
+      <c r="F55" s="8">
         <v>0.04</v>
       </c>
       <c r="G55" s="4" t="s">
@@ -3156,10 +2869,10 @@
       <c r="H55" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I55" s="9">
-        <v>0</v>
-      </c>
-      <c r="J55" s="9">
+      <c r="I55" s="8">
+        <v>0</v>
+      </c>
+      <c r="J55" s="8">
         <v>0</v>
       </c>
       <c r="K55" s="4" t="s">
@@ -3183,22 +2896,22 @@
       <c r="D56" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E56" s="10">
+      <c r="E56" s="9">
         <v>2888</v>
       </c>
-      <c r="F56" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G56" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H56" s="7">
+      <c r="F56" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G56" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H56" s="5">
         <v>29</v>
       </c>
-      <c r="I56" s="9">
-        <v>0</v>
-      </c>
-      <c r="J56" s="9">
+      <c r="I56" s="8">
+        <v>0</v>
+      </c>
+      <c r="J56" s="8">
         <v>0</v>
       </c>
       <c r="K56" s="4" t="s">
@@ -3222,22 +2935,22 @@
       <c r="D57" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E57" s="10">
+      <c r="E57" s="9">
         <v>2199</v>
       </c>
-      <c r="F57" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G57" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H57" s="7">
-        <v>22</v>
-      </c>
-      <c r="I57" s="7">
+      <c r="F57" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G57" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H57" s="5">
+        <v>22</v>
+      </c>
+      <c r="I57" s="5">
         <v>19</v>
       </c>
-      <c r="J57" s="7">
+      <c r="J57" s="5">
         <v>19</v>
       </c>
       <c r="K57" s="4" t="s">
@@ -3246,7 +2959,7 @@
       <c r="L57" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M57" s="5"/>
+      <c r="M57" s="7"/>
     </row>
     <row r="58" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A58" s="4" t="s">
@@ -3261,22 +2974,22 @@
       <c r="D58" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E58" s="7">
+      <c r="E58" s="5">
         <v>186</v>
       </c>
-      <c r="F58" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="G58" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H58" s="8">
+      <c r="F58" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="G58" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="H58" s="6">
         <v>1.9</v>
       </c>
-      <c r="I58" s="8">
+      <c r="I58" s="6">
         <v>0.3</v>
       </c>
-      <c r="J58" s="8">
+      <c r="J58" s="6">
         <v>0.3</v>
       </c>
       <c r="K58" s="4" t="s">
@@ -3288,6 +3001,7 @@
       <c r="M58" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M58" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>